--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -475,7 +475,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cholemetric AI — Android E2E Test Report — Passed Test Cases — 2026-08-09 23:23:23</t>
+          <t>Cholemetric AI — Android E2E Test Report — Passed Test Cases — 2026-08-09 23:37:25</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -475,7 +475,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cholemetric AI — Android E2E Test Report — Passed Test Cases — 2026-08-09 23:37:25</t>
+          <t>Cholemetric AI — Android E2E Test Report — Passed Test Cases — 2026-08-10 00:14:30</t>
         </is>
       </c>
     </row>
